--- a/data/Blumenau/Julho 2025 - Bistek Garcia.xlsx
+++ b/data/Blumenau/Julho 2025 - Bistek Garcia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2cd8c5b933a682c/Área de Trabalho/Cidadania Financeira/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://furb-my.sharepoint.com/personal/bttomio_furb_br/Documents/Documentos/GitHub/CidadaniaFinanceira/data/Blumenau/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{3C232C63-CEC1-4BB5-87A0-6840DE2C42E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D5AF66D-E5FF-4D86-B7C1-F19B1AA2C043}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{3C232C63-CEC1-4BB5-87A0-6840DE2C42E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D684EF9A-6F44-4C7F-9084-D34070636C9E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="63">
   <si>
     <t>MERCADO</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Bistek - Garcia</t>
+  </si>
+  <si>
+    <t>Julho/2025</t>
   </si>
 </sst>
 </file>
@@ -822,70 +825,70 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -957,10 +960,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1227,24 +1226,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.6640625" style="1"/>
-    <col min="13" max="13" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.6640625" style="1"/>
+    <col min="7" max="7" width="27.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.7109375" style="1"/>
+    <col min="13" max="13" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1255,7 +1254,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="5"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1266,7 +1265,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1277,7 +1276,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1288,26 +1287,26 @@
       <c r="H4" s="10"/>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="45"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="46">
-        <v>45844</v>
-      </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
+      <c r="E5" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
       <c r="H5" s="14"/>
       <c r="I5" s="15"/>
     </row>
-    <row r="6" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>2</v>
       </c>
@@ -1320,27 +1319,27 @@
       <c r="D6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="51"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="42">
         <v>1</v>
       </c>
       <c r="E7" s="19" t="s">
@@ -1355,15 +1354,15 @@
       <c r="H7" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="33">
         <v>3.74</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="34"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
+    <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="53"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="22" t="s">
         <v>12</v>
       </c>
@@ -1376,19 +1375,19 @@
       <c r="H8" s="24">
         <v>4.16</v>
       </c>
-      <c r="I8" s="48"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="37" t="s">
+      <c r="I8" s="34"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="52">
         <v>1</v>
       </c>
       <c r="E9" s="25" t="s">
@@ -1403,15 +1402,15 @@
       <c r="H9" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="53">
+      <c r="I9" s="36">
         <v>4.47</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="38"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
+    <row r="10" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="50"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="28" t="s">
         <v>12</v>
       </c>
@@ -1424,19 +1423,19 @@
       <c r="H10" s="30">
         <v>4.95</v>
       </c>
-      <c r="I10" s="54"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="33" t="s">
+      <c r="I10" s="37"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="42">
         <v>0.5</v>
       </c>
       <c r="E11" s="19" t="s">
@@ -1451,15 +1450,15 @@
       <c r="H11" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="33">
         <v>27.97</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="34"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
+    <row r="12" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="53"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
       <c r="E12" s="22" t="s">
         <v>12</v>
       </c>
@@ -1472,19 +1471,19 @@
       <c r="H12" s="24">
         <v>29</v>
       </c>
-      <c r="I12" s="48"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="37" t="s">
+      <c r="I12" s="34"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="52">
         <v>1</v>
       </c>
       <c r="E13" s="25" t="s">
@@ -1499,15 +1498,15 @@
       <c r="H13" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="53">
+      <c r="I13" s="36">
         <v>3.97</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="38"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
+    <row r="14" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="50"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="28" t="s">
         <v>12</v>
       </c>
@@ -1520,19 +1519,19 @@
       <c r="H14" s="30">
         <v>3.95</v>
       </c>
-      <c r="I14" s="54"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="33" t="s">
+      <c r="I14" s="37"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="42">
         <v>1</v>
       </c>
       <c r="E15" s="19" t="s">
@@ -1547,15 +1546,15 @@
       <c r="H15" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="47">
+      <c r="I15" s="33">
         <v>5.2766666669999998</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="34"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
+    <row r="16" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="53"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
       <c r="E16" s="22" t="s">
         <v>12</v>
       </c>
@@ -1568,19 +1567,19 @@
       <c r="H16" s="24">
         <v>4.99</v>
       </c>
-      <c r="I16" s="48"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="37" t="s">
+      <c r="I16" s="34"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="52">
         <v>0.5</v>
       </c>
       <c r="E17" s="25" t="s">
@@ -1595,15 +1594,15 @@
       <c r="H17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="I17" s="53">
+      <c r="I17" s="36">
         <v>29.08666667</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="38"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
+    <row r="18" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="50"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
       <c r="E18" s="28" t="s">
         <v>12</v>
       </c>
@@ -1616,19 +1615,19 @@
       <c r="H18" s="30">
         <v>29.97</v>
       </c>
-      <c r="I18" s="54"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="33" t="s">
+      <c r="I18" s="37"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="42">
         <v>0.9</v>
       </c>
       <c r="E19" s="19" t="s">
@@ -1643,15 +1642,15 @@
       <c r="H19" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="47">
+      <c r="I19" s="33">
         <v>6.89</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="34"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
+    <row r="20" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="53"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
       <c r="E20" s="22" t="s">
         <v>12</v>
       </c>
@@ -1664,19 +1663,19 @@
       <c r="H20" s="24">
         <v>6.9</v>
       </c>
-      <c r="I20" s="48"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="37" t="s">
+      <c r="I20" s="34"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="52">
         <v>1</v>
       </c>
       <c r="E21" s="25" t="s">
@@ -1691,15 +1690,15 @@
       <c r="H21" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="53">
+      <c r="I21" s="36">
         <v>45.563333329999999</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="38"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
+    <row r="22" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="50"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
       <c r="E22" s="28" t="s">
         <v>12</v>
       </c>
@@ -1712,19 +1711,19 @@
       <c r="H22" s="30">
         <v>48.01</v>
       </c>
-      <c r="I22" s="54"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
+      <c r="I22" s="37"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="42">
         <v>1</v>
       </c>
       <c r="E23" s="19" t="s">
@@ -1735,15 +1734,15 @@
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="47">
+      <c r="I23" s="33">
         <v>15.93</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="34"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
+    <row r="24" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="53"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
       <c r="E24" s="22" t="s">
         <v>12</v>
       </c>
@@ -1752,19 +1751,19 @@
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="24"/>
-      <c r="I24" s="48"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="37" t="s">
+      <c r="I24" s="34"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="52">
         <v>1</v>
       </c>
       <c r="E25" s="25" t="s">
@@ -1775,15 +1774,15 @@
       </c>
       <c r="G25" s="26"/>
       <c r="H25" s="27"/>
-      <c r="I25" s="53">
+      <c r="I25" s="36">
         <v>7.75</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="38"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
+    <row r="26" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="50"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="28" t="s">
         <v>12</v>
       </c>
@@ -1792,19 +1791,19 @@
       </c>
       <c r="G26" s="29"/>
       <c r="H26" s="30"/>
-      <c r="I26" s="54"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
+      <c r="I26" s="37"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="42">
         <v>1</v>
       </c>
       <c r="E27" s="19" t="s">
@@ -1815,15 +1814,15 @@
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="21"/>
-      <c r="I27" s="47">
+      <c r="I27" s="33">
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
+    <row r="28" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="45"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
       <c r="E28" s="22" t="s">
         <v>12</v>
       </c>
@@ -1832,19 +1831,19 @@
       </c>
       <c r="G28" s="23"/>
       <c r="H28" s="24"/>
-      <c r="I28" s="48"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="44" t="s">
+      <c r="I28" s="34"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="43" t="s">
+      <c r="C29" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="43">
+      <c r="D29" s="47">
         <v>1</v>
       </c>
       <c r="E29" s="25" t="s">
@@ -1859,15 +1858,15 @@
       <c r="H29" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="I29" s="53">
+      <c r="I29" s="36">
         <v>4.47</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="38"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
+    <row r="30" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="50"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
       <c r="E30" s="22" t="s">
         <v>12</v>
       </c>
@@ -1880,19 +1879,19 @@
       <c r="H30" s="32">
         <v>4.5</v>
       </c>
-      <c r="I30" s="54"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="33" t="s">
+      <c r="I30" s="37"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="42">
         <v>1</v>
       </c>
       <c r="E31" s="19" t="s">
@@ -1903,15 +1902,15 @@
       </c>
       <c r="G31" s="20"/>
       <c r="H31" s="21"/>
-      <c r="I31" s="47">
+      <c r="I31" s="33">
         <v>3.97</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="42"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
+    <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="45"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
       <c r="E32" s="22" t="s">
         <v>12</v>
       </c>
@@ -1920,49 +1919,23 @@
       </c>
       <c r="G32" s="23"/>
       <c r="H32" s="24"/>
-      <c r="I32" s="52"/>
+      <c r="I32" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="C15:C16"/>
@@ -1979,19 +1952,45 @@
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I29:I30"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
